--- a/NominalSheet.xlsx
+++ b/NominalSheet.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="84">
   <si>
     <t xml:space="preserve">Ill CSE I A Section ( B.Tech, 2022 Batch ) I MID Examination Marks Award List, 2024-25</t>
   </si>
@@ -625,11 +625,11 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="9" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="7" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="9" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -637,7 +637,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="5" shrinkToFit="true"/>
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="7" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -763,9 +763,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>180360</xdr:colOff>
+      <xdr:colOff>180000</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>10800</xdr:rowOff>
+      <xdr:rowOff>10440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -779,7 +779,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="170640" y="9012600"/>
-          <a:ext cx="9720" cy="13680"/>
+          <a:ext cx="9360" cy="13320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -800,9 +800,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>84240</xdr:colOff>
+      <xdr:colOff>83880</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>10800</xdr:rowOff>
+      <xdr:rowOff>10440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -816,7 +816,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="887040" y="9012600"/>
-          <a:ext cx="9720" cy="13680"/>
+          <a:ext cx="9360" cy="13320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -837,9 +837,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>44280</xdr:colOff>
+      <xdr:colOff>43920</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>10800</xdr:rowOff>
+      <xdr:rowOff>10440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -853,7 +853,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2451240" y="9012600"/>
-          <a:ext cx="9720" cy="13680"/>
+          <a:ext cx="9360" cy="13320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -874,9 +874,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>225000</xdr:colOff>
+      <xdr:colOff>224640</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>10800</xdr:rowOff>
+      <xdr:rowOff>10440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -890,7 +890,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2831760" y="9012600"/>
-          <a:ext cx="9720" cy="13680"/>
+          <a:ext cx="9360" cy="13320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -911,9 +911,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>184320</xdr:colOff>
+      <xdr:colOff>183960</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>10800</xdr:rowOff>
+      <xdr:rowOff>10440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -927,7 +927,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3223080" y="9012600"/>
-          <a:ext cx="9720" cy="13680"/>
+          <a:ext cx="9360" cy="13320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -948,9 +948,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>111240</xdr:colOff>
+      <xdr:colOff>110880</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>10800</xdr:rowOff>
+      <xdr:rowOff>10440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -964,7 +964,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3602880" y="9012600"/>
-          <a:ext cx="9720" cy="13680"/>
+          <a:ext cx="9360" cy="13320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -985,9 +985,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>462960</xdr:colOff>
+      <xdr:colOff>462600</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>10800</xdr:rowOff>
+      <xdr:rowOff>10440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1001,7 +1001,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4882320" y="9012600"/>
-          <a:ext cx="9720" cy="13680"/>
+          <a:ext cx="9360" cy="13320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1022,9 +1022,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>825120</xdr:colOff>
+      <xdr:colOff>824760</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>187920</xdr:rowOff>
+      <xdr:rowOff>187560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1038,7 +1038,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="170640" y="9012600"/>
-          <a:ext cx="7450200" cy="190800"/>
+          <a:ext cx="7449840" cy="190440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1059,9 +1059,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>711360</xdr:colOff>
+      <xdr:colOff>711000</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>227160</xdr:rowOff>
+      <xdr:rowOff>226800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1075,7 +1075,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3960" y="1958760"/>
-          <a:ext cx="707400" cy="9360"/>
+          <a:ext cx="707040" cy="9000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1096,9 +1096,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1463760</xdr:colOff>
+      <xdr:colOff>1463400</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>227160</xdr:rowOff>
+      <xdr:rowOff>226800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1112,7 +1112,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720000" y="1958760"/>
-          <a:ext cx="1556280" cy="9360"/>
+          <a:ext cx="1555920" cy="9000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1133,9 +1133,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>39600</xdr:colOff>
+      <xdr:colOff>39240</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>227160</xdr:rowOff>
+      <xdr:rowOff>226800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1149,7 +1149,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2285280" y="1958760"/>
-          <a:ext cx="370800" cy="9360"/>
+          <a:ext cx="370440" cy="9000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1170,9 +1170,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>431280</xdr:colOff>
+      <xdr:colOff>430920</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>227160</xdr:rowOff>
+      <xdr:rowOff>226800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1186,7 +1186,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2664720" y="1958760"/>
-          <a:ext cx="383040" cy="9360"/>
+          <a:ext cx="382680" cy="9000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1207,9 +1207,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>379800</xdr:colOff>
+      <xdr:colOff>379440</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>227160</xdr:rowOff>
+      <xdr:rowOff>226800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1223,7 +1223,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3056040" y="1958760"/>
-          <a:ext cx="372240" cy="9360"/>
+          <a:ext cx="371880" cy="9000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1244,9 +1244,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>356040</xdr:colOff>
+      <xdr:colOff>355680</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>227160</xdr:rowOff>
+      <xdr:rowOff>226800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1260,7 +1260,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3437280" y="1958760"/>
-          <a:ext cx="420120" cy="9360"/>
+          <a:ext cx="419760" cy="9000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1281,9 +1281,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>276480</xdr:colOff>
+      <xdr:colOff>276120</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>227160</xdr:rowOff>
+      <xdr:rowOff>226800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1297,7 +1297,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3867480" y="1958760"/>
-          <a:ext cx="838080" cy="9360"/>
+          <a:ext cx="837720" cy="9000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1318,9 +1318,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>496440</xdr:colOff>
+      <xdr:colOff>496080</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>227160</xdr:rowOff>
+      <xdr:rowOff>226800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1334,7 +1334,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4715640" y="1958760"/>
-          <a:ext cx="1193400" cy="9360"/>
+          <a:ext cx="1193040" cy="9000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1355,9 +1355,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>640080</xdr:colOff>
+      <xdr:colOff>639720</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>227160</xdr:rowOff>
+      <xdr:rowOff>226800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1371,7 +1371,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5917320" y="1958760"/>
-          <a:ext cx="1518480" cy="9360"/>
+          <a:ext cx="1518120" cy="9000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1392,9 +1392,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>711720</xdr:colOff>
+      <xdr:colOff>711360</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>222120</xdr:rowOff>
+      <xdr:rowOff>221760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1408,7 +1408,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3960" y="2406600"/>
-          <a:ext cx="707760" cy="10080"/>
+          <a:ext cx="707400" cy="9720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1429,9 +1429,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1464120</xdr:colOff>
+      <xdr:colOff>1463760</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>222120</xdr:rowOff>
+      <xdr:rowOff>221760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1445,7 +1445,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720000" y="2406600"/>
-          <a:ext cx="1556640" cy="10080"/>
+          <a:ext cx="1556280" cy="9720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1466,9 +1466,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>39960</xdr:colOff>
+      <xdr:colOff>39600</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>222120</xdr:rowOff>
+      <xdr:rowOff>221760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1482,7 +1482,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2285640" y="2406600"/>
-          <a:ext cx="370800" cy="10080"/>
+          <a:ext cx="370440" cy="9720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1503,9 +1503,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>431640</xdr:colOff>
+      <xdr:colOff>431280</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>222120</xdr:rowOff>
+      <xdr:rowOff>221760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1519,7 +1519,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2665080" y="2406600"/>
-          <a:ext cx="383040" cy="10080"/>
+          <a:ext cx="382680" cy="9720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1540,9 +1540,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>380160</xdr:colOff>
+      <xdr:colOff>379800</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>222120</xdr:rowOff>
+      <xdr:rowOff>221760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1556,7 +1556,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3056400" y="2406600"/>
-          <a:ext cx="372240" cy="10080"/>
+          <a:ext cx="371880" cy="9720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1577,9 +1577,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>844920</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>1080</xdr:rowOff>
+      <xdr:colOff>844560</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>222120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1593,7 +1593,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4435200" y="2406600"/>
-          <a:ext cx="838800" cy="10440"/>
+          <a:ext cx="838440" cy="10080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1614,9 +1614,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>711360</xdr:colOff>
+      <xdr:colOff>711000</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>221040</xdr:rowOff>
+      <xdr:rowOff>220680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1630,7 +1630,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3960" y="3303000"/>
-          <a:ext cx="707400" cy="9000"/>
+          <a:ext cx="707040" cy="8640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1651,9 +1651,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1463760</xdr:colOff>
+      <xdr:colOff>1463400</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>221040</xdr:rowOff>
+      <xdr:rowOff>220680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1667,7 +1667,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720000" y="3303000"/>
-          <a:ext cx="1556280" cy="9000"/>
+          <a:ext cx="1555920" cy="8640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1688,9 +1688,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>39600</xdr:colOff>
+      <xdr:colOff>39240</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>221040</xdr:rowOff>
+      <xdr:rowOff>220680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1704,7 +1704,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2285280" y="3303000"/>
-          <a:ext cx="370800" cy="9000"/>
+          <a:ext cx="370440" cy="8640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1725,9 +1725,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>431280</xdr:colOff>
+      <xdr:colOff>430920</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>221040</xdr:rowOff>
+      <xdr:rowOff>220680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1741,7 +1741,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2664720" y="3303000"/>
-          <a:ext cx="383040" cy="9000"/>
+          <a:ext cx="382680" cy="8640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1762,9 +1762,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>379800</xdr:colOff>
+      <xdr:colOff>379440</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>221040</xdr:rowOff>
+      <xdr:rowOff>220680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1778,7 +1778,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3056040" y="3303000"/>
-          <a:ext cx="372240" cy="9000"/>
+          <a:ext cx="371880" cy="8640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1799,9 +1799,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>356040</xdr:colOff>
+      <xdr:colOff>355680</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>221040</xdr:rowOff>
+      <xdr:rowOff>220680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1815,7 +1815,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3437280" y="3303000"/>
-          <a:ext cx="420120" cy="9000"/>
+          <a:ext cx="419760" cy="8640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1836,9 +1836,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>276480</xdr:colOff>
+      <xdr:colOff>276120</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>221040</xdr:rowOff>
+      <xdr:rowOff>220680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1852,7 +1852,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3867480" y="3303000"/>
-          <a:ext cx="838080" cy="9000"/>
+          <a:ext cx="837720" cy="8640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1873,9 +1873,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>496440</xdr:colOff>
+      <xdr:colOff>496080</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>221040</xdr:rowOff>
+      <xdr:rowOff>220680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1889,7 +1889,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4715640" y="3303000"/>
-          <a:ext cx="1193400" cy="9000"/>
+          <a:ext cx="1193040" cy="8640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1910,9 +1910,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>640080</xdr:colOff>
+      <xdr:colOff>639720</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>221040</xdr:rowOff>
+      <xdr:rowOff>220680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1926,7 +1926,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5917320" y="3303000"/>
-          <a:ext cx="1518480" cy="9000"/>
+          <a:ext cx="1518120" cy="8640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1947,9 +1947,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>711360</xdr:colOff>
+      <xdr:colOff>711000</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>6840</xdr:rowOff>
+      <xdr:rowOff>6480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1963,7 +1963,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3960" y="4425480"/>
-          <a:ext cx="707400" cy="9720"/>
+          <a:ext cx="707040" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1984,9 +1984,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1463760</xdr:colOff>
+      <xdr:colOff>1463400</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>6840</xdr:rowOff>
+      <xdr:rowOff>6480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2000,7 +2000,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720000" y="4425480"/>
-          <a:ext cx="1556280" cy="9720"/>
+          <a:ext cx="1555920" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2021,9 +2021,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>39600</xdr:colOff>
+      <xdr:colOff>39240</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>6840</xdr:rowOff>
+      <xdr:rowOff>6480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2037,7 +2037,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2285280" y="4425480"/>
-          <a:ext cx="370800" cy="9720"/>
+          <a:ext cx="370440" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2058,9 +2058,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>431280</xdr:colOff>
+      <xdr:colOff>430920</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>6840</xdr:rowOff>
+      <xdr:rowOff>6480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2074,7 +2074,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2664720" y="4425480"/>
-          <a:ext cx="383040" cy="9720"/>
+          <a:ext cx="382680" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2095,9 +2095,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>379800</xdr:colOff>
+      <xdr:colOff>379440</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>6840</xdr:rowOff>
+      <xdr:rowOff>6480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2111,7 +2111,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3056040" y="4425480"/>
-          <a:ext cx="372240" cy="9720"/>
+          <a:ext cx="371880" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2132,9 +2132,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>356040</xdr:colOff>
+      <xdr:colOff>355680</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>6840</xdr:rowOff>
+      <xdr:rowOff>6480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2148,7 +2148,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3437280" y="4425480"/>
-          <a:ext cx="420120" cy="9720"/>
+          <a:ext cx="419760" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2169,9 +2169,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>276480</xdr:colOff>
+      <xdr:colOff>276120</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>6840</xdr:rowOff>
+      <xdr:rowOff>6480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2185,7 +2185,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3867480" y="4425480"/>
-          <a:ext cx="838080" cy="9720"/>
+          <a:ext cx="837720" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2206,9 +2206,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>496440</xdr:colOff>
+      <xdr:colOff>496080</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>6840</xdr:rowOff>
+      <xdr:rowOff>6480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2222,7 +2222,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4715640" y="4425480"/>
-          <a:ext cx="1193400" cy="9720"/>
+          <a:ext cx="1193040" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2243,9 +2243,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>640080</xdr:colOff>
+      <xdr:colOff>639720</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>6840</xdr:rowOff>
+      <xdr:rowOff>6480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2259,7 +2259,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5917320" y="4425480"/>
-          <a:ext cx="1518480" cy="9720"/>
+          <a:ext cx="1518120" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2276,11 +2276,11 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>3960</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>185400</xdr:rowOff>
+      <xdr:rowOff>185760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>711720</xdr:colOff>
+      <xdr:colOff>711360</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>4680</xdr:rowOff>
     </xdr:to>
@@ -2295,8 +2295,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3960" y="5728680"/>
-          <a:ext cx="707760" cy="9720"/>
+          <a:off x="3960" y="5729040"/>
+          <a:ext cx="707400" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2311,9 +2311,9 @@
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>4680</xdr:colOff>
+      <xdr:colOff>5040</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>185400</xdr:rowOff>
+      <xdr:rowOff>185760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -2332,8 +2332,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="817200" y="5728680"/>
-          <a:ext cx="1556280" cy="9720"/>
+          <a:off x="817560" y="5729040"/>
+          <a:ext cx="1555920" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2348,9 +2348,9 @@
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>4680</xdr:colOff>
+      <xdr:colOff>5040</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>185400</xdr:rowOff>
+      <xdr:rowOff>185760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
@@ -2369,8 +2369,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2621160" y="5728680"/>
-          <a:ext cx="372240" cy="9720"/>
+          <a:off x="2621520" y="5729040"/>
+          <a:ext cx="371880" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2387,11 +2387,11 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>4320</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>185400</xdr:rowOff>
+      <xdr:rowOff>185760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>387360</xdr:colOff>
+      <xdr:colOff>387000</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>4680</xdr:rowOff>
     </xdr:to>
@@ -2406,8 +2406,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3052800" y="5728680"/>
-          <a:ext cx="383040" cy="9720"/>
+          <a:off x="3052800" y="5729040"/>
+          <a:ext cx="382680" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2424,11 +2424,11 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>4680</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>185400</xdr:rowOff>
+      <xdr:rowOff>185760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>376920</xdr:colOff>
+      <xdr:colOff>376560</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>4680</xdr:rowOff>
     </xdr:to>
@@ -2443,8 +2443,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3506040" y="5728680"/>
-          <a:ext cx="372240" cy="9720"/>
+          <a:off x="3506040" y="5729040"/>
+          <a:ext cx="371880" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2459,9 +2459,9 @@
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>3960</xdr:colOff>
+      <xdr:colOff>4320</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>185400</xdr:rowOff>
+      <xdr:rowOff>185760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
@@ -2480,8 +2480,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3936960" y="5728680"/>
-          <a:ext cx="421200" cy="9720"/>
+          <a:off x="3937320" y="5729040"/>
+          <a:ext cx="420840" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2498,11 +2498,11 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>6120</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>185400</xdr:rowOff>
+      <xdr:rowOff>185760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>844920</xdr:colOff>
+      <xdr:colOff>844560</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>4680</xdr:rowOff>
     </xdr:to>
@@ -2517,8 +2517,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4435200" y="5728680"/>
-          <a:ext cx="838800" cy="9720"/>
+          <a:off x="4435200" y="5729040"/>
+          <a:ext cx="838440" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2535,11 +2535,11 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>3960</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>185400</xdr:rowOff>
+      <xdr:rowOff>185760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1196280</xdr:colOff>
+      <xdr:colOff>1195920</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>4680</xdr:rowOff>
     </xdr:to>
@@ -2554,8 +2554,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5416560" y="5728680"/>
-          <a:ext cx="1192320" cy="9720"/>
+          <a:off x="5416560" y="5729040"/>
+          <a:ext cx="1191960" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2572,11 +2572,11 @@
       <xdr:col>9</xdr:col>
       <xdr:colOff>3960</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>185400</xdr:rowOff>
+      <xdr:rowOff>185760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1522440</xdr:colOff>
+      <xdr:colOff>1522080</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>4680</xdr:rowOff>
     </xdr:to>
@@ -2591,8 +2591,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6799680" y="5728680"/>
-          <a:ext cx="1518480" cy="9720"/>
+          <a:off x="6799680" y="5729040"/>
+          <a:ext cx="1518120" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2613,9 +2613,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>221760</xdr:colOff>
+      <xdr:colOff>221400</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>151920</xdr:rowOff>
+      <xdr:rowOff>151560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2625,7 +2625,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3214800" y="2041560"/>
-          <a:ext cx="55440" cy="78120"/>
+          <a:ext cx="55080" cy="77760"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -2776,9 +2776,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>212400</xdr:colOff>
+      <xdr:colOff>212040</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>154080</xdr:rowOff>
+      <xdr:rowOff>153720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2788,7 +2788,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3668400" y="2041560"/>
-          <a:ext cx="45360" cy="80280"/>
+          <a:ext cx="45000" cy="79920"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -2930,11 +2930,11 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>164160</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>72000</xdr:rowOff>
+      <xdr:rowOff>72360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>215280</xdr:colOff>
+      <xdr:colOff>214920</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>153360</xdr:rowOff>
     </xdr:to>
@@ -2945,8 +2945,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3665520" y="2487960"/>
-          <a:ext cx="51120" cy="81360"/>
+          <a:off x="3665520" y="2488320"/>
+          <a:ext cx="50760" cy="81000"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -3245,7 +3245,7 @@
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>165960</xdr:colOff>
+      <xdr:colOff>166320</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>70920</xdr:rowOff>
     </xdr:from>
@@ -3253,7 +3253,7 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>213840</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>152280</xdr:rowOff>
+      <xdr:rowOff>151920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3262,8 +3262,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2782440" y="3383640"/>
-          <a:ext cx="47880" cy="81360"/>
+          <a:off x="2782800" y="3383640"/>
+          <a:ext cx="47520" cy="81000"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -3506,9 +3506,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>214920</xdr:colOff>
+      <xdr:colOff>214560</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>152640</xdr:rowOff>
+      <xdr:rowOff>152280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3518,7 +3518,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3660840" y="3385080"/>
-          <a:ext cx="55440" cy="80280"/>
+          <a:ext cx="55080" cy="79920"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -3657,7 +3657,7 @@
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>159840</xdr:colOff>
+      <xdr:colOff>160200</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>80280</xdr:rowOff>
     </xdr:from>
@@ -3665,7 +3665,7 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>215280</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>160560</xdr:rowOff>
+      <xdr:rowOff>160200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3674,8 +3674,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2776320" y="4508640"/>
-          <a:ext cx="55440" cy="80280"/>
+          <a:off x="2776680" y="4508640"/>
+          <a:ext cx="55080" cy="79920"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -3826,9 +3826,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>212400</xdr:colOff>
+      <xdr:colOff>212040</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>161640</xdr:rowOff>
+      <xdr:rowOff>161280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3838,7 +3838,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3668400" y="4508640"/>
-          <a:ext cx="45360" cy="81360"/>
+          <a:ext cx="45000" cy="81000"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -4019,9 +4019,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>448560</xdr:colOff>
+      <xdr:colOff>448200</xdr:colOff>
       <xdr:row>67</xdr:row>
-      <xdr:rowOff>153000</xdr:rowOff>
+      <xdr:rowOff>152640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4035,7 +4035,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4833000" y="15540120"/>
-          <a:ext cx="44640" cy="81360"/>
+          <a:ext cx="44280" cy="81000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4056,9 +4056,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>711360</xdr:colOff>
+      <xdr:colOff>711000</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>9360</xdr:rowOff>
+      <xdr:rowOff>9000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4072,7 +4072,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3960" y="9423000"/>
-          <a:ext cx="707400" cy="9720"/>
+          <a:ext cx="707040" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4093,9 +4093,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1463760</xdr:colOff>
+      <xdr:colOff>1463400</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>9360</xdr:rowOff>
+      <xdr:rowOff>9000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4109,7 +4109,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720000" y="9423000"/>
-          <a:ext cx="1556280" cy="9720"/>
+          <a:ext cx="1555920" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4130,9 +4130,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>39600</xdr:colOff>
+      <xdr:colOff>39240</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>9360</xdr:rowOff>
+      <xdr:rowOff>9000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4146,7 +4146,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2285280" y="9423000"/>
-          <a:ext cx="370800" cy="9720"/>
+          <a:ext cx="370440" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4167,9 +4167,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>431280</xdr:colOff>
+      <xdr:colOff>430920</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>9360</xdr:rowOff>
+      <xdr:rowOff>9000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4183,7 +4183,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2664720" y="9423000"/>
-          <a:ext cx="383040" cy="9720"/>
+          <a:ext cx="382680" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4204,9 +4204,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>379800</xdr:colOff>
+      <xdr:colOff>379440</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>9360</xdr:rowOff>
+      <xdr:rowOff>9000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4220,7 +4220,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3056040" y="9423000"/>
-          <a:ext cx="372240" cy="9720"/>
+          <a:ext cx="371880" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4241,9 +4241,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>356040</xdr:colOff>
+      <xdr:colOff>355680</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>9360</xdr:rowOff>
+      <xdr:rowOff>9000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4257,7 +4257,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3437280" y="9423000"/>
-          <a:ext cx="420120" cy="9720"/>
+          <a:ext cx="419760" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4278,9 +4278,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>276480</xdr:colOff>
+      <xdr:colOff>276120</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>9360</xdr:rowOff>
+      <xdr:rowOff>9000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4294,7 +4294,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3867480" y="9423000"/>
-          <a:ext cx="838080" cy="9720"/>
+          <a:ext cx="837720" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4315,9 +4315,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>496440</xdr:colOff>
+      <xdr:colOff>496080</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>9360</xdr:rowOff>
+      <xdr:rowOff>9000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4331,7 +4331,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4715640" y="9423000"/>
-          <a:ext cx="1193400" cy="9720"/>
+          <a:ext cx="1193040" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4352,9 +4352,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>640080</xdr:colOff>
+      <xdr:colOff>639720</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>9360</xdr:rowOff>
+      <xdr:rowOff>9000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4368,7 +4368,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5917320" y="9423000"/>
-          <a:ext cx="1518480" cy="9720"/>
+          <a:ext cx="1518120" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4389,9 +4389,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>711360</xdr:colOff>
+      <xdr:colOff>711000</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>225360</xdr:rowOff>
+      <xdr:rowOff>225000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4405,7 +4405,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3960" y="10537560"/>
-          <a:ext cx="707400" cy="9720"/>
+          <a:ext cx="707040" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4426,9 +4426,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1463760</xdr:colOff>
+      <xdr:colOff>1463400</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>225360</xdr:rowOff>
+      <xdr:rowOff>225000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4442,7 +4442,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="720000" y="10537560"/>
-          <a:ext cx="1556280" cy="9720"/>
+          <a:ext cx="1555920" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4463,9 +4463,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>39600</xdr:colOff>
+      <xdr:colOff>39240</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>225360</xdr:rowOff>
+      <xdr:rowOff>225000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4479,7 +4479,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2285280" y="10537560"/>
-          <a:ext cx="370800" cy="9720"/>
+          <a:ext cx="370440" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4500,9 +4500,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>431280</xdr:colOff>
+      <xdr:colOff>430920</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>225360</xdr:rowOff>
+      <xdr:rowOff>225000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4516,7 +4516,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2664720" y="10537560"/>
-          <a:ext cx="383040" cy="9720"/>
+          <a:ext cx="382680" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4537,9 +4537,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>379800</xdr:colOff>
+      <xdr:colOff>379440</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>225360</xdr:rowOff>
+      <xdr:rowOff>225000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4553,7 +4553,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3056040" y="10537560"/>
-          <a:ext cx="372240" cy="9720"/>
+          <a:ext cx="371880" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4574,9 +4574,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>356040</xdr:colOff>
+      <xdr:colOff>355680</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>225360</xdr:rowOff>
+      <xdr:rowOff>225000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4590,7 +4590,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3437280" y="10537560"/>
-          <a:ext cx="420120" cy="9720"/>
+          <a:ext cx="419760" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4611,9 +4611,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>276480</xdr:colOff>
+      <xdr:colOff>276120</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>225360</xdr:rowOff>
+      <xdr:rowOff>225000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4627,7 +4627,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3867480" y="10537560"/>
-          <a:ext cx="838080" cy="9720"/>
+          <a:ext cx="837720" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4648,9 +4648,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>496440</xdr:colOff>
+      <xdr:colOff>496080</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>225360</xdr:rowOff>
+      <xdr:rowOff>225000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4664,7 +4664,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4715640" y="10537560"/>
-          <a:ext cx="1193400" cy="9720"/>
+          <a:ext cx="1193040" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4685,9 +4685,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>640080</xdr:colOff>
+      <xdr:colOff>639720</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>225360</xdr:rowOff>
+      <xdr:rowOff>225000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4701,7 +4701,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5917320" y="10537560"/>
-          <a:ext cx="1518480" cy="9720"/>
+          <a:ext cx="1518120" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4722,9 +4722,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>221760</xdr:colOff>
+      <xdr:colOff>221400</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>167040</xdr:rowOff>
+      <xdr:rowOff>166680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4734,7 +4734,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3214800" y="9507240"/>
-          <a:ext cx="55440" cy="83160"/>
+          <a:ext cx="55080" cy="82800"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -4882,9 +4882,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>210960</xdr:colOff>
+      <xdr:colOff>210600</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>168120</xdr:rowOff>
+      <xdr:rowOff>167760</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4894,7 +4894,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3666960" y="9507240"/>
-          <a:ext cx="45360" cy="84240"/>
+          <a:ext cx="45000" cy="83880"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -5096,11 +5096,11 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>172440</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>73080</xdr:rowOff>
+      <xdr:rowOff>73440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>217800</xdr:colOff>
+      <xdr:colOff>217440</xdr:colOff>
       <xdr:row>45</xdr:row>
       <xdr:rowOff>154440</xdr:rowOff>
     </xdr:to>
@@ -5111,8 +5111,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3220920" y="10621440"/>
-          <a:ext cx="45360" cy="81360"/>
+          <a:off x="3220920" y="10621800"/>
+          <a:ext cx="45000" cy="81000"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -5334,11 +5334,11 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>164160</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>73080</xdr:rowOff>
+      <xdr:rowOff>73440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>213840</xdr:colOff>
+      <xdr:colOff>213480</xdr:colOff>
       <xdr:row>45</xdr:row>
       <xdr:rowOff>153360</xdr:rowOff>
     </xdr:to>
@@ -5349,8 +5349,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3665520" y="10621440"/>
-          <a:ext cx="49680" cy="80280"/>
+          <a:off x="3665520" y="10621800"/>
+          <a:ext cx="49320" cy="79920"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -5585,9 +5585,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>639720</xdr:colOff>
+      <xdr:colOff>639360</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>1690200</xdr:rowOff>
+      <xdr:rowOff>1689840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5597,7 +5597,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="170640" y="1157400"/>
-          <a:ext cx="5918400" cy="1344960"/>
+          <a:ext cx="5918040" cy="1344600"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -5666,9 +5666,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>792720</xdr:colOff>
+      <xdr:colOff>792360</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>353520</xdr:rowOff>
+      <xdr:rowOff>353160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5682,7 +5682,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="170640" y="709560"/>
-          <a:ext cx="7454520" cy="456120"/>
+          <a:ext cx="7454160" cy="455760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5703,9 +5703,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>180360</xdr:colOff>
+      <xdr:colOff>180000</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>802800</xdr:rowOff>
+      <xdr:rowOff>802440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5719,7 +5719,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="170640" y="1386000"/>
-          <a:ext cx="9720" cy="228960"/>
+          <a:ext cx="9360" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5740,9 +5740,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>896760</xdr:colOff>
+      <xdr:colOff>896400</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>802800</xdr:rowOff>
+      <xdr:rowOff>802440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5756,7 +5756,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="887040" y="1386000"/>
-          <a:ext cx="9720" cy="228960"/>
+          <a:ext cx="9360" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5777,9 +5777,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>2461680</xdr:colOff>
+      <xdr:colOff>2461320</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>802800</xdr:rowOff>
+      <xdr:rowOff>802440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5793,7 +5793,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2451960" y="1386000"/>
-          <a:ext cx="9720" cy="228960"/>
+          <a:ext cx="9360" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5814,9 +5814,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>2842920</xdr:colOff>
+      <xdr:colOff>2842560</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>802800</xdr:rowOff>
+      <xdr:rowOff>802440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5830,7 +5830,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2833200" y="1386000"/>
-          <a:ext cx="9720" cy="228960"/>
+          <a:ext cx="9360" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5851,9 +5851,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>3234600</xdr:colOff>
+      <xdr:colOff>3234240</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>802800</xdr:rowOff>
+      <xdr:rowOff>802440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5867,7 +5867,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3224880" y="1386000"/>
-          <a:ext cx="9720" cy="228960"/>
+          <a:ext cx="9360" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5888,9 +5888,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>3615480</xdr:colOff>
+      <xdr:colOff>3615120</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>802800</xdr:rowOff>
+      <xdr:rowOff>802440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5904,7 +5904,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3605760" y="1386000"/>
-          <a:ext cx="9720" cy="228960"/>
+          <a:ext cx="9360" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5925,9 +5925,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>430200</xdr:colOff>
+      <xdr:colOff>429840</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>802800</xdr:rowOff>
+      <xdr:rowOff>802440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5941,7 +5941,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4886280" y="1386000"/>
-          <a:ext cx="9720" cy="228960"/>
+          <a:ext cx="9360" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5962,9 +5962,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>792720</xdr:colOff>
+      <xdr:colOff>792360</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>1470240</xdr:rowOff>
+      <xdr:rowOff>1469880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5978,7 +5978,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="170640" y="1386000"/>
-          <a:ext cx="7454520" cy="896400"/>
+          <a:ext cx="7454160" cy="896040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5999,9 +5999,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>180360</xdr:colOff>
+      <xdr:colOff>180000</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>1918800</xdr:rowOff>
+      <xdr:rowOff>1918440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6015,7 +6015,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="170640" y="2512440"/>
-          <a:ext cx="9720" cy="218520"/>
+          <a:ext cx="9360" cy="218160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6036,9 +6036,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>896760</xdr:colOff>
+      <xdr:colOff>896400</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>1918800</xdr:rowOff>
+      <xdr:rowOff>1918440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6052,7 +6052,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="887040" y="2512440"/>
-          <a:ext cx="9720" cy="218520"/>
+          <a:ext cx="9360" cy="218160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6073,9 +6073,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>2461680</xdr:colOff>
+      <xdr:colOff>2461320</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>1918800</xdr:rowOff>
+      <xdr:rowOff>1918440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6089,7 +6089,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2451960" y="2512440"/>
-          <a:ext cx="9720" cy="218520"/>
+          <a:ext cx="9360" cy="218160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6110,9 +6110,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>2842920</xdr:colOff>
+      <xdr:colOff>2842560</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>1918800</xdr:rowOff>
+      <xdr:rowOff>1918440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6126,7 +6126,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2833200" y="2512440"/>
-          <a:ext cx="9720" cy="218520"/>
+          <a:ext cx="9360" cy="218160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6147,9 +6147,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>3234600</xdr:colOff>
+      <xdr:colOff>3234240</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>1918800</xdr:rowOff>
+      <xdr:rowOff>1918440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6163,7 +6163,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3224880" y="2512440"/>
-          <a:ext cx="9720" cy="218520"/>
+          <a:ext cx="9360" cy="218160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6184,9 +6184,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>3615480</xdr:colOff>
+      <xdr:colOff>3615120</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>1918800</xdr:rowOff>
+      <xdr:rowOff>1918440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6200,7 +6200,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3605760" y="2512440"/>
-          <a:ext cx="9720" cy="218520"/>
+          <a:ext cx="9360" cy="218160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6221,9 +6221,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>430200</xdr:colOff>
+      <xdr:colOff>429840</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>1918800</xdr:rowOff>
+      <xdr:rowOff>1918440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6237,7 +6237,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4886280" y="2512440"/>
-          <a:ext cx="9720" cy="218520"/>
+          <a:ext cx="9360" cy="218160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6258,9 +6258,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>792720</xdr:colOff>
+      <xdr:colOff>792360</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>3231360</xdr:rowOff>
+      <xdr:rowOff>3231000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6274,7 +6274,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="170640" y="2512440"/>
-          <a:ext cx="7454520" cy="6724440"/>
+          <a:ext cx="7454160" cy="6724080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6295,9 +6295,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>3430440</xdr:colOff>
+      <xdr:colOff>3430080</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>9720</xdr:rowOff>
+      <xdr:rowOff>9360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6311,7 +6311,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3960" y="0"/>
-          <a:ext cx="3426480" cy="9720"/>
+          <a:ext cx="3426120" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6326,7 +6326,7 @@
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>4680</xdr:colOff>
+      <xdr:colOff>5040</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -6334,7 +6334,7 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>425880</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>9720</xdr:rowOff>
+      <xdr:rowOff>9360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6347,8 +6347,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3974400" y="0"/>
-          <a:ext cx="421200" cy="9720"/>
+          <a:off x="3974760" y="0"/>
+          <a:ext cx="420840" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6369,9 +6369,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>844200</xdr:colOff>
+      <xdr:colOff>843840</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>9720</xdr:rowOff>
+      <xdr:rowOff>9360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6385,7 +6385,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4471200" y="0"/>
-          <a:ext cx="838800" cy="9720"/>
+          <a:ext cx="838440" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6400,7 +6400,7 @@
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>4320</xdr:colOff>
+      <xdr:colOff>4680</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -6408,7 +6408,7 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>1196640</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>9720</xdr:rowOff>
+      <xdr:rowOff>9360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6421,8 +6421,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5453640" y="0"/>
-          <a:ext cx="1192320" cy="9720"/>
+          <a:off x="5454000" y="0"/>
+          <a:ext cx="1191960" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6443,9 +6443,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1523160</xdr:colOff>
+      <xdr:colOff>1522800</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>9720</xdr:rowOff>
+      <xdr:rowOff>9360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6459,7 +6459,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6837120" y="0"/>
-          <a:ext cx="1518480" cy="9720"/>
+          <a:ext cx="1518120" cy="9360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6480,9 +6480,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>3387240</xdr:colOff>
+      <xdr:colOff>3386880</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>159840</xdr:rowOff>
+      <xdr:rowOff>159480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6496,7 +6496,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2993040" y="120600"/>
-          <a:ext cx="394200" cy="105840"/>
+          <a:ext cx="393840" cy="105480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6517,7 +6517,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L1048576"/>
-  <sheetFormatPr defaultColWidth="8.703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.32"/>
@@ -8520,95 +8520,9 @@
       </c>
       <c r="K71" s="9"/>
     </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C72" s="1"/>
-      <c r="D72" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E72" s="20"/>
-      <c r="F72" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G72" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H72" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="I72" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J72" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="K72" s="7"/>
-    </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C73" s="1"/>
-      <c r="D73" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E73" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="F73" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G73" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H73" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="I73" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J73" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="K73" s="7"/>
-    </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C74" s="1"/>
-      <c r="D74" s="20"/>
-      <c r="E74" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F74" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G74" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H74" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="I74" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J74" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="K74" s="9"/>
-    </row>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -8616,7 +8530,7 @@
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="133">
+  <mergeCells count="127">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="B3:C3"/>
@@ -8744,12 +8658,6 @@
     <mergeCell ref="J70:K70"/>
     <mergeCell ref="B71:C71"/>
     <mergeCell ref="J71:K71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="J72:K72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="J73:K73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="J74:K74"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -8768,7 +8676,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G1048576"/>
-  <sheetFormatPr defaultColWidth="8.703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="3.83"/>
@@ -8838,9 +8746,9 @@
     </row>
     <row r="5" customFormat="false" ht="408.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="263.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
